--- a/results/02_taxa_assemblage/MRT_Method/ModelD_AllSites/tables/mrt_cp_table.xlsx
+++ b/results/02_taxa_assemblage/MRT_Method/ModelD_AllSites/tables/mrt_cp_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.09471436314363146</v>
+        <v>0.1219533875338754</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -479,16 +479,16 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.935483870967742</v>
+        <v>1.057894736842105</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01862420223192341</v>
+        <v>0.02536286367508941</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8459677419354839</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="H2" t="n">
-        <v>1.025</v>
+        <v>1.157894736842105</v>
       </c>
     </row>
     <row r="3">
@@ -496,25 +496,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.09016341463414629</v>
+        <v>0.06955070603337615</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9096774193548388</v>
+        <v>1.042105263157895</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01720430107526882</v>
+        <v>0.04493420517496737</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8459677419354839</v>
+        <v>0.8657894736842104</v>
       </c>
       <c r="H3" t="n">
-        <v>0.992741935483871</v>
+        <v>1.292105263157895</v>
       </c>
     </row>
     <row r="4">
@@ -522,25 +522,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0625</v>
+        <v>0.05823558897243111</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9129032258064516</v>
+        <v>1.052631578947369</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03567883875921948</v>
+        <v>0.04574878880843965</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7241935483870968</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="H4" t="n">
-        <v>1.032258064516129</v>
+        <v>1.332894736842105</v>
       </c>
     </row>
     <row r="5">
@@ -548,25 +548,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.05166666666666667</v>
+        <v>0.04723809523809519</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4516129032258064</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8838709677419354</v>
+        <v>1.057894736842105</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02812192866800434</v>
+        <v>0.04927919966732681</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.906578947368421</v>
       </c>
       <c r="H5" t="n">
-        <v>1.017741935483871</v>
+        <v>1.373684210526316</v>
       </c>
     </row>
     <row r="6">
@@ -574,25 +574,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.04715</v>
+        <v>0.03733333333333336</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8774193548387096</v>
+        <v>1.115789473684211</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03108996192430314</v>
+        <v>0.03310168818265475</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7491935483870967</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1.042741935483871</v>
+        <v>1.292105263157895</v>
       </c>
     </row>
     <row r="7">
@@ -603,22 +603,22 @@
         <v>0.03555555555555555</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8709677419354838</v>
+        <v>1.105263157894737</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04301075268817205</v>
+        <v>0.03138341021052337</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7241935483870968</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.135483870967742</v>
+        <v>1.292105263157895</v>
       </c>
     </row>
     <row r="8">
@@ -626,25 +626,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.015</v>
+        <v>0.02666666666666666</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8612903225806452</v>
+        <v>1.105263157894737</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04638635400026451</v>
+        <v>0.03138341021052337</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6919354838709677</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.153225806451613</v>
+        <v>1.292105263157895</v>
       </c>
     </row>
     <row r="9">
@@ -652,25 +652,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01392857142857142</v>
+        <v>0.02333333333333333</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="E9" t="n">
-        <v>0.867741935483871</v>
+        <v>1.094736842105263</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04623655913978494</v>
+        <v>0.02456140350877193</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6919354838709677</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.153225806451613</v>
+        <v>1.210526315789474</v>
       </c>
     </row>
     <row r="10">
@@ -678,129 +678,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01333333333333333</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2258064516129032</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="E10" t="n">
-        <v>0.867741935483871</v>
+        <v>1.121052631578947</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04623655913978494</v>
+        <v>0.01929824561403509</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6919354838709677</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="H10" t="n">
-        <v>1.153225806451613</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.01199999999999999</v>
-      </c>
-      <c r="C11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.2258064516129032</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.867741935483871</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.04623655913978494</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.6919354838709677</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.153225806451613</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.01190476190476192</v>
-      </c>
-      <c r="C12" t="n">
-        <v>11</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.2258064516129032</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.867741935483871</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.04623655913978494</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.6919354838709677</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.153225806451613</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.008333333333333333</v>
-      </c>
-      <c r="C13" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.2258064516129032</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.867741935483871</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.04623655913978494</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.6919354838709677</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.153225806451613</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>14</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.2258064516129032</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.867741935483871</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.04623655913978494</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.6919354838709677</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.153225806451613</v>
+        <v>1.210526315789474</v>
       </c>
     </row>
   </sheetData>
